--- a/Mod_Korean/Lang/KR/Game/Calc.xlsx
+++ b/Mod_Korean/Lang/KR/Game/Calc.xlsx
@@ -26,7 +26,7 @@
     <t xml:space="preserve">SpHolyVeil</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.237 Patch 1</t>
+    <t xml:space="preserve">EA 23.247</t>
   </si>
   <si>
     <t xml:space="preserve">SpHero</t>

--- a/Mod_Korean/Lang/KR/Game/Calc.xlsx
+++ b/Mod_Korean/Lang/KR/Game/Calc.xlsx
@@ -26,7 +26,7 @@
     <t xml:space="preserve">SpHolyVeil</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.247</t>
+    <t xml:space="preserve">EA 23.252</t>
   </si>
   <si>
     <t xml:space="preserve">SpHero</t>

--- a/Mod_Korean/Lang/KR/Game/Calc.xlsx
+++ b/Mod_Korean/Lang/KR/Game/Calc.xlsx
@@ -26,7 +26,7 @@
     <t xml:space="preserve">SpHolyVeil</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.252</t>
+    <t xml:space="preserve">EA 23.260</t>
   </si>
   <si>
     <t xml:space="preserve">SpHero</t>

--- a/Mod_Korean/Lang/KR/Game/Calc.xlsx
+++ b/Mod_Korean/Lang/KR/Game/Calc.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="52">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -26,7 +26,7 @@
     <t xml:space="preserve">SpHolyVeil</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.260</t>
+    <t xml:space="preserve">EA 23.267</t>
   </si>
   <si>
     <t xml:space="preserve">SpHero</t>
@@ -66,6 +66,9 @@
   </si>
   <si>
     <t xml:space="preserve">sword_</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SpTelekinesis</t>
   </si>
   <si>
     <t xml:space="preserve">SpMoonArrow</t>
@@ -243,7 +246,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4">
@@ -251,7 +254,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5">
@@ -259,7 +262,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6">
@@ -267,7 +270,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7">
@@ -275,7 +278,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8">
@@ -283,7 +286,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9">
@@ -291,7 +294,7 @@
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10">
@@ -299,7 +302,7 @@
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11">
@@ -307,7 +310,7 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12">
@@ -315,7 +318,7 @@
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13">
@@ -323,7 +326,7 @@
         <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14">
@@ -331,7 +334,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15">
@@ -339,7 +342,7 @@
         <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16">
@@ -347,7 +350,7 @@
         <v>16</v>
       </c>
       <c r="B16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17">
@@ -355,7 +358,7 @@
         <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>45</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -371,7 +374,7 @@
         <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20">
@@ -379,7 +382,7 @@
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21">
@@ -395,7 +398,7 @@
         <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23">
@@ -403,7 +406,7 @@
         <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="24">
@@ -411,7 +414,7 @@
         <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
     </row>
     <row r="25">
@@ -419,7 +422,7 @@
         <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="26">
@@ -427,7 +430,7 @@
         <v>26</v>
       </c>
       <c r="B26" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="27">
@@ -435,7 +438,7 @@
         <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="28">
@@ -443,7 +446,7 @@
         <v>28</v>
       </c>
       <c r="B28" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="29">
@@ -451,7 +454,7 @@
         <v>29</v>
       </c>
       <c r="B29" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="30">
@@ -459,7 +462,7 @@
         <v>30</v>
       </c>
       <c r="B30" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
     </row>
     <row r="31">
@@ -475,7 +478,7 @@
         <v>32</v>
       </c>
       <c r="B32" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="33">
@@ -483,7 +486,7 @@
         <v>33</v>
       </c>
       <c r="B33" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="34">
@@ -491,7 +494,7 @@
         <v>34</v>
       </c>
       <c r="B34" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="35">
@@ -507,7 +510,7 @@
         <v>36</v>
       </c>
       <c r="B36" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="37">
@@ -515,7 +518,7 @@
         <v>37</v>
       </c>
       <c r="B37" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="38">
@@ -523,7 +526,15 @@
         <v>38</v>
       </c>
       <c r="B38" t="s">
-        <v>50</v>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>39</v>
+      </c>
+      <c r="B39" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/Mod_Korean/Lang/KR/Game/Calc.xlsx
+++ b/Mod_Korean/Lang/KR/Game/Calc.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="53">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -26,133 +26,136 @@
     <t xml:space="preserve">SpHolyVeil</t>
   </si>
   <si>
+    <t xml:space="preserve">EA 23.281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SpHero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SpCatsEye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ActLulwyTrick</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DrainBlood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DrainMana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">breathe_</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ball_</t>
+  </si>
+  <si>
+    <t xml:space="preserve">flare_</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bolt_</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hand_</t>
+  </si>
+  <si>
+    <t xml:space="preserve">arrow_</t>
+  </si>
+  <si>
+    <t xml:space="preserve">miasma_</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sword_</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SpTelekinesis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SpMoonArrow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SpMoonSpear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SpMeteor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SpEarthquake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SpShutterHex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SpSilence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SpHealLight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SpHealHeavy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SpHealCritical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SpHeal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SpHealEris</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SpHealOdina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SpHealJure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SpHOT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ActManaAbsorb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ActJureHeal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">funnel_</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ActSummonGodPet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ActSummonUndeadSister</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SpTeleport</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SpReturn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SpEvac</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alpha 16.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alpha 18.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EA 23.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EA 23.74</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EA 23.222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EA 23.120</t>
+  </si>
+  <si>
     <t xml:space="preserve">EA 23.267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SpHero</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SpCatsEye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ActLulwyTrick</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DrainBlood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DrainMana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">breathe_</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ball_</t>
-  </si>
-  <si>
-    <t xml:space="preserve">flare_</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bolt_</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hand_</t>
-  </si>
-  <si>
-    <t xml:space="preserve">arrow_</t>
-  </si>
-  <si>
-    <t xml:space="preserve">miasma_</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sword_</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SpTelekinesis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SpMoonArrow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SpMoonSpear</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SpMeteor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SpEarthquake</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SpShutterHex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SpSilence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SpHealLight</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SpHealHeavy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SpHealCritical</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SpHeal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SpHealEris</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SpHealOdina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SpHealJure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SpHOT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ActManaAbsorb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ActJureHeal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">funnel_</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ActSummonGodPet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ActSummonUndeadSister</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SpTeleport</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SpReturn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SpEvac</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alpha 16.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alpha 18.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EA 23.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EA 23.74</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EA 23.222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EA 23.120</t>
   </si>
   <si>
     <t xml:space="preserve">EA 23.209 Patch 2</t>
@@ -358,7 +361,7 @@
         <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>3</v>
+        <v>46</v>
       </c>
     </row>
     <row r="18">
@@ -366,7 +369,7 @@
         <v>18</v>
       </c>
       <c r="B18" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19">
@@ -374,7 +377,7 @@
         <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20">
@@ -390,7 +393,7 @@
         <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22">
@@ -398,7 +401,7 @@
         <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23">
@@ -422,7 +425,7 @@
         <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="26">
@@ -430,7 +433,7 @@
         <v>26</v>
       </c>
       <c r="B26" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="27">
@@ -438,7 +441,7 @@
         <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="28">
@@ -446,7 +449,7 @@
         <v>28</v>
       </c>
       <c r="B28" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="29">
@@ -454,7 +457,7 @@
         <v>29</v>
       </c>
       <c r="B29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="30">
@@ -462,7 +465,7 @@
         <v>30</v>
       </c>
       <c r="B30" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="31">
@@ -534,7 +537,7 @@
         <v>39</v>
       </c>
       <c r="B39" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>

--- a/Mod_Korean/Lang/KR/Game/Calc.xlsx
+++ b/Mod_Korean/Lang/KR/Game/Calc.xlsx
@@ -26,7 +26,7 @@
     <t xml:space="preserve">SpHolyVeil</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.281</t>
+    <t xml:space="preserve">EA 23.282 Patch 2</t>
   </si>
   <si>
     <t xml:space="preserve">SpHero</t>

--- a/Mod_Korean/Lang/KR/Game/Calc.xlsx
+++ b/Mod_Korean/Lang/KR/Game/Calc.xlsx
@@ -26,7 +26,7 @@
     <t xml:space="preserve">SpHolyVeil</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.282 Patch 2</t>
+    <t xml:space="preserve">EA 23.287</t>
   </si>
   <si>
     <t xml:space="preserve">SpHero</t>

--- a/Mod_Korean/Lang/KR/Game/Calc.xlsx
+++ b/Mod_Korean/Lang/KR/Game/Calc.xlsx
@@ -26,7 +26,7 @@
     <t xml:space="preserve">SpHolyVeil</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.287</t>
+    <t xml:space="preserve">EA 23.295</t>
   </si>
   <si>
     <t xml:space="preserve">SpHero</t>

--- a/Mod_Korean/Lang/KR/Game/Calc.xlsx
+++ b/Mod_Korean/Lang/KR/Game/Calc.xlsx
@@ -26,7 +26,7 @@
     <t xml:space="preserve">SpHolyVeil</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.295</t>
+    <t xml:space="preserve">EA 23.307</t>
   </si>
   <si>
     <t xml:space="preserve">SpHero</t>

--- a/Mod_Korean/Lang/KR/Game/Calc.xlsx
+++ b/Mod_Korean/Lang/KR/Game/Calc.xlsx
@@ -26,7 +26,7 @@
     <t xml:space="preserve">SpHolyVeil</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.307</t>
+    <t xml:space="preserve">EA 23.325</t>
   </si>
   <si>
     <t xml:space="preserve">SpHero</t>

--- a/Mod_Korean/Lang/KR/Game/Calc.xlsx
+++ b/Mod_Korean/Lang/KR/Game/Calc.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="54">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -26,7 +26,7 @@
     <t xml:space="preserve">SpHolyVeil</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.325</t>
+    <t xml:space="preserve">EA 23.338 Patch 2</t>
   </si>
   <si>
     <t xml:space="preserve">SpHero</t>
@@ -51,6 +51,9 @@
   </si>
   <si>
     <t xml:space="preserve">flare_</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comet_</t>
   </si>
   <si>
     <t xml:space="preserve">bolt_</t>
@@ -249,7 +252,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4">
@@ -257,7 +260,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5">
@@ -265,7 +268,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6">
@@ -273,7 +276,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7">
@@ -281,7 +284,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8">
@@ -289,7 +292,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9">
@@ -297,7 +300,7 @@
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10">
@@ -305,7 +308,7 @@
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11">
@@ -313,7 +316,7 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12">
@@ -321,7 +324,7 @@
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>40</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -329,7 +332,7 @@
         <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14">
@@ -337,7 +340,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15">
@@ -345,7 +348,7 @@
         <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16">
@@ -353,7 +356,7 @@
         <v>16</v>
       </c>
       <c r="B16" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17">
@@ -385,7 +388,7 @@
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21">
@@ -393,7 +396,7 @@
         <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
     </row>
     <row r="22">
@@ -409,7 +412,7 @@
         <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
     </row>
     <row r="24">
@@ -417,7 +420,7 @@
         <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="25">
@@ -425,7 +428,7 @@
         <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
     </row>
     <row r="26">
@@ -433,7 +436,7 @@
         <v>26</v>
       </c>
       <c r="B26" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="27">
@@ -441,7 +444,7 @@
         <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="28">
@@ -449,7 +452,7 @@
         <v>28</v>
       </c>
       <c r="B28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="29">
@@ -457,7 +460,7 @@
         <v>29</v>
       </c>
       <c r="B29" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="30">
@@ -465,7 +468,7 @@
         <v>30</v>
       </c>
       <c r="B30" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="31">
@@ -473,7 +476,7 @@
         <v>31</v>
       </c>
       <c r="B31" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
     </row>
     <row r="32">
@@ -489,7 +492,7 @@
         <v>33</v>
       </c>
       <c r="B33" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="34">
@@ -497,7 +500,7 @@
         <v>34</v>
       </c>
       <c r="B34" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="35">
@@ -505,7 +508,7 @@
         <v>35</v>
       </c>
       <c r="B35" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="36">
@@ -521,7 +524,7 @@
         <v>37</v>
       </c>
       <c r="B37" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="38">
@@ -529,7 +532,7 @@
         <v>38</v>
       </c>
       <c r="B38" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="39">
@@ -537,7 +540,15 @@
         <v>39</v>
       </c>
       <c r="B39" t="s">
-        <v>52</v>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>40</v>
+      </c>
+      <c r="B40" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
